--- a/static/uploads/discente.xlsx
+++ b/static/uploads/discente.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thatt\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321D3C75-962A-425A-A94A-79E600C2FDC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3450C66E-369E-46FD-94FF-F0F0C82DB20E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1EFD2A4C-C4EE-4571-AEC1-FBA7DFEEB730}"/>
   </bookViews>
@@ -25,52 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="93">
-  <si>
-    <t>2. Qual o seu ano de ingresso?</t>
-  </si>
-  <si>
-    <t>3. A qual programa está vinculado?</t>
-  </si>
-  <si>
-    <t>Como você avalia a qualidade das aulas e do material utilizado?  [Qualidade das aulas]</t>
-  </si>
-  <si>
-    <t>Como você avalia a qualidade das aulas e do material utilizado?  [Material didático utilizado nas disciplinas]</t>
-  </si>
-  <si>
-    <t>Como você avalia a qualidade das aulas e do material utilizado?  [Acervo disponível para consulta]</t>
-  </si>
-  <si>
-    <t>Como você avalia a  infraestrutura do programa?  [Infraestrutura geral]</t>
-  </si>
-  <si>
-    <t>Como você avalia a  infraestrutura do programa?  [Laboratórios de pesquisa/Salas de estudo]</t>
-  </si>
-  <si>
-    <t>Como você avalia a  infraestrutura do programa?  [Insumos para pesquisa]</t>
-  </si>
-  <si>
-    <t>Como você avalia o relacionamento entre você e: [os colegas]</t>
-  </si>
-  <si>
-    <t>Como você avalia o relacionamento entre você e: [a comissão orientadora]</t>
-  </si>
-  <si>
-    <t>Como você avalia o relacionamento entre você e: [a comissão coordenadora]</t>
-  </si>
-  <si>
-    <t>Como você avalia o relacionamento entre você e: [a secretaria do programa]</t>
-  </si>
-  <si>
-    <t>Como você avalia a gestão do programa? [Processo de gestão/Administrativo do Programa]</t>
-  </si>
-  <si>
-    <t>Como você avalia a gestão do programa? [Organização do Programa]</t>
-  </si>
-  <si>
-    <t>Como você avalia o seu conhecimento acerca: [do seu papel enquanto aluno]</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="91">
   <si>
     <t>Como você avalia o seu conhecimento acerca: [do Regimento Interno do Programa]</t>
   </si>
@@ -78,9 +33,6 @@
     <t>Como você avalia o seu conhecimento acerca: [do Regimento Geral da Pós-Graduação]</t>
   </si>
   <si>
-    <t>Como você avalia o seu conhecimento acerca: [das normas da Capes]</t>
-  </si>
-  <si>
     <t>Como você avalia o seu conhecimento acerca: [do processo de avaliação da Capes]</t>
   </si>
   <si>
@@ -138,33 +90,12 @@
     <t>Você já apresentou algum resultado de sua pesquisa em algum evento voltado para a COMUNIDADE, ou pretende apresentar?</t>
   </si>
   <si>
-    <t>Você já apresentou algum resultado de sua pesquisa em algum evento CIENTÍFICO, ou pretende apresentar?</t>
-  </si>
-  <si>
     <t>Sua pesquisa poderá gerar soluções para os problemas que a sociedade enfrenta ou virá a enfrentar?</t>
   </si>
   <si>
-    <t>Qual o principal impacto social a ser promovido por seu projeto de pesquisa? (Marque todas aplicáveis)</t>
-  </si>
-  <si>
     <t>Qual o nível de internacionalização do seu programa?</t>
   </si>
   <si>
-    <t>No momento, há interesse por parte do seu Programa de Pós-Graduação em iniciar um processo de Internacionalização?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Você se sente preparado para a internacionalização do seu Programa de Pós-Graduação? </t>
-  </si>
-  <si>
-    <t>Você entende que o seu Programa de Pós-Graduação está preparado para a internacionalização?</t>
-  </si>
-  <si>
-    <t>Seu projeto de pesquisa possui parcerias com instituições internacionais de pesquisa ou ensino?</t>
-  </si>
-  <si>
-    <t>Qual o seu nível de proficiência em língua inglesa?</t>
-  </si>
-  <si>
     <t>Ciência da Computação</t>
   </si>
   <si>
@@ -304,6 +235,69 @@
   </si>
   <si>
     <t>Acho que um melhor direcionamento sobre publicações, para que isso não fique só a cargo do orientador. Os integrantes do programa como um todo deveriam colaborar com informações sobre como proceder com as publicações</t>
+  </si>
+  <si>
+    <t>programa</t>
+  </si>
+  <si>
+    <t>ano_ingresso</t>
+  </si>
+  <si>
+    <t>Qualidade das aulas</t>
+  </si>
+  <si>
+    <t>Material didático utilizado nas disciplinas</t>
+  </si>
+  <si>
+    <t>Acervo disponível para consulta</t>
+  </si>
+  <si>
+    <t>Infraestrutura geral</t>
+  </si>
+  <si>
+    <t>Relacionamento os colegas</t>
+  </si>
+  <si>
+    <t>relacionamento entre você a secretaria do programa</t>
+  </si>
+  <si>
+    <t>Processo de gestão/Administrativo do Programa</t>
+  </si>
+  <si>
+    <t>Organização do Programa</t>
+  </si>
+  <si>
+    <t>Seu conhecimento como aluno</t>
+  </si>
+  <si>
+    <t>Como você avalia o seu conhecimento sas normas da Capes</t>
+  </si>
+  <si>
+    <t>parcerias com instituições internacionais de pesquisa ou ensino</t>
+  </si>
+  <si>
+    <t>interesse por parte do seu Programa de Pós-Graduação em processo de Internacionalização</t>
+  </si>
+  <si>
+    <t>Qual o principal impacto social do projeto de pesquisa</t>
+  </si>
+  <si>
+    <t>Você já apresentou algum resultado de sua pesquisa em algum evento CIENTÍFICO</t>
+  </si>
+  <si>
+    <t>Insumos para pesquisa</t>
+  </si>
+  <si>
+    <t>Laboratorios Salas de estudo</t>
+  </si>
+  <si>
+    <t>Nivel de ingles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Você está preparado para internacionalização programa </t>
+  </si>
+  <si>
+    <t>O Programa está preparado para a internacionalização</t>
   </si>
 </sst>
 </file>
@@ -662,166 +656,161 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58F2F859-14FA-45B0-A91F-E519FDFC0A04}">
-  <dimension ref="A1:AT27"/>
+  <dimension ref="A1:AR27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" customWidth="1"/>
-    <col min="2" max="2" width="20.44140625" customWidth="1"/>
-    <col min="3" max="3" width="16.21875" customWidth="1"/>
-    <col min="4" max="4" width="14.21875" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" customWidth="1"/>
-    <col min="44" max="44" width="39.88671875" customWidth="1"/>
-    <col min="45" max="45" width="52.109375" customWidth="1"/>
-    <col min="46" max="46" width="41.44140625" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" customWidth="1"/>
+    <col min="2" max="2" width="19.21875" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="24.44140625" customWidth="1"/>
+    <col min="5" max="5" width="27" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" customWidth="1"/>
+    <col min="7" max="7" width="40.21875" customWidth="1"/>
+    <col min="42" max="42" width="34.21875" customWidth="1"/>
+    <col min="43" max="43" width="52.109375" customWidth="1"/>
+    <col min="44" max="44" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="AN1" s="1" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>2020</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1">
         <v>5</v>
@@ -848,16 +837,16 @@
         <v>4</v>
       </c>
       <c r="K2" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M2" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N2" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O2" s="1">
         <v>4</v>
@@ -881,84 +870,78 @@
         <v>4</v>
       </c>
       <c r="V2" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W2" s="1">
-        <v>4</v>
-      </c>
-      <c r="X2" s="1">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="Y2" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA2" s="1">
-        <v>4</v>
+        <v>25</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK2" s="1" t="s">
-        <v>53</v>
+        <v>30</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>4</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="AM2" s="1">
         <v>4</v>
       </c>
-      <c r="AN2" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="AO2" s="1">
-        <v>4</v>
-      </c>
-      <c r="AQ2" s="1">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>3</v>
+      </c>
+      <c r="AQ2" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AR2" s="1">
-        <v>3</v>
-      </c>
-      <c r="AS2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT2" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2020</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
@@ -982,7 +965,7 @@
         <v>5</v>
       </c>
       <c r="J3" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K3" s="1">
         <v>4</v>
@@ -991,7 +974,7 @@
         <v>4</v>
       </c>
       <c r="M3" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N3" s="1">
         <v>4</v>
@@ -1000,96 +983,90 @@
         <v>3</v>
       </c>
       <c r="P3" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R3" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S3" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T3" s="1">
         <v>4</v>
       </c>
       <c r="U3" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V3" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W3" s="1">
         <v>4</v>
       </c>
-      <c r="X3" s="1">
-        <v>3</v>
-      </c>
-      <c r="Y3" s="1">
-        <v>4</v>
+      <c r="X3" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>52</v>
+        <v>32</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AC3" s="1" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="AJ3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK3" s="1" t="s">
-        <v>52</v>
+        <v>34</v>
+      </c>
+      <c r="AK3" s="1">
+        <v>4</v>
       </c>
       <c r="AL3" s="1" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AM3" s="1">
-        <v>4</v>
-      </c>
-      <c r="AN3" s="1" t="s">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="AO3" s="1">
         <v>2</v>
       </c>
-      <c r="AQ3" s="1">
-        <v>2</v>
+      <c r="AP3" s="1">
+        <v>4</v>
+      </c>
+      <c r="AQ3" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AR3" s="1">
-        <v>4</v>
-      </c>
-      <c r="AS3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AT3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2020</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1">
         <v>5</v>
@@ -1137,90 +1114,84 @@
         <v>5</v>
       </c>
       <c r="R4" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S4" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U4" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V4" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W4" s="1">
         <v>5</v>
       </c>
-      <c r="X4" s="1">
-        <v>2</v>
+      <c r="X4" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="Y4" s="1">
         <v>5</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA4" s="1">
-        <v>5</v>
+        <v>36</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC4" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="AD4" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AF4" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="AG4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH4" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="AI4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK4" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK4" s="1">
+        <v>5</v>
       </c>
       <c r="AL4" s="1" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="AM4" s="1">
         <v>5</v>
       </c>
-      <c r="AN4" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="AO4" s="1">
         <v>5</v>
       </c>
-      <c r="AQ4" s="1">
-        <v>5</v>
+      <c r="AP4" s="1">
+        <v>5</v>
+      </c>
+      <c r="AQ4" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AR4" s="1">
         <v>5</v>
       </c>
-      <c r="AS4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT4" s="1">
-        <v>5</v>
-      </c>
     </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>2020</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1">
         <v>5</v>
@@ -1259,13 +1230,13 @@
         <v>5</v>
       </c>
       <c r="O5" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P5" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q5" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R5" s="1">
         <v>4</v>
@@ -1274,84 +1245,78 @@
         <v>3</v>
       </c>
       <c r="T5" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U5" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V5" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W5" s="1">
         <v>5</v>
       </c>
-      <c r="X5" s="1">
-        <v>4</v>
-      </c>
-      <c r="Y5" s="1">
-        <v>5</v>
+      <c r="X5" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>52</v>
+        <v>37</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC5" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="AD5" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
+      </c>
+      <c r="AE5" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AF5" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="AG5" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="AH5" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="AI5" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="AJ5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK5" s="1" t="s">
-        <v>52</v>
+        <v>34</v>
+      </c>
+      <c r="AK5" s="1">
+        <v>4</v>
       </c>
       <c r="AL5" s="1" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="AM5" s="1">
         <v>4</v>
       </c>
-      <c r="AN5" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="AO5" s="1">
-        <v>4</v>
-      </c>
-      <c r="AQ5" s="1">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="AP5" s="1">
+        <v>5</v>
+      </c>
+      <c r="AQ5" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AR5" s="1">
         <v>5</v>
       </c>
-      <c r="AS5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AT5" s="1">
-        <v>5</v>
-      </c>
     </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2020</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1">
         <v>4</v>
@@ -1375,7 +1340,7 @@
         <v>5</v>
       </c>
       <c r="J6" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" s="1">
         <v>4</v>
@@ -1390,25 +1355,25 @@
         <v>3</v>
       </c>
       <c r="O6" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R6" s="1">
         <v>4</v>
       </c>
       <c r="S6" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T6" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U6" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V6" s="1">
         <v>5</v>
@@ -1416,76 +1381,70 @@
       <c r="W6" s="1">
         <v>5</v>
       </c>
-      <c r="X6" s="1">
-        <v>5</v>
+      <c r="X6" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="Y6" s="1">
         <v>5</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA6" s="1">
-        <v>5</v>
+        <v>39</v>
+      </c>
+      <c r="AA6" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC6" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="AD6" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
+      </c>
+      <c r="AE6" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AF6" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="AG6" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="AH6" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="AI6" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="AJ6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK6" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
+      </c>
+      <c r="AK6" s="1">
+        <v>5</v>
       </c>
       <c r="AL6" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AM6" s="1">
         <v>5</v>
       </c>
-      <c r="AN6" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="AO6" s="1">
-        <v>5</v>
-      </c>
-      <c r="AQ6" s="1">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="AP6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AQ6" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AR6" s="1">
-        <v>4</v>
-      </c>
-      <c r="AS6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AT6" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2020</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1">
         <v>4</v>
@@ -1509,7 +1468,7 @@
         <v>5</v>
       </c>
       <c r="J7" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K7" s="1">
         <v>4</v>
@@ -1524,25 +1483,25 @@
         <v>3</v>
       </c>
       <c r="O7" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P7" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q7" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R7" s="1">
         <v>4</v>
       </c>
       <c r="S7" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T7" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U7" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V7" s="1">
         <v>5</v>
@@ -1550,76 +1509,70 @@
       <c r="W7" s="1">
         <v>5</v>
       </c>
-      <c r="X7" s="1">
-        <v>5</v>
+      <c r="X7" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="Y7" s="1">
         <v>5</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA7" s="1">
-        <v>5</v>
+        <v>39</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC7" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
+      </c>
+      <c r="AE7" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AF7" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="AG7" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="AH7" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="AI7" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK7" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
+      </c>
+      <c r="AK7" s="1">
+        <v>5</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AM7" s="1">
         <v>5</v>
       </c>
-      <c r="AN7" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="AO7" s="1">
-        <v>5</v>
-      </c>
-      <c r="AQ7" s="1">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="AP7" s="1">
+        <v>4</v>
+      </c>
+      <c r="AQ7" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AR7" s="1">
-        <v>4</v>
-      </c>
-      <c r="AS7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AT7" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>2018</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1">
         <v>5</v>
@@ -1655,370 +1608,352 @@
         <v>5</v>
       </c>
       <c r="N8" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O8" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P8" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S8" s="1">
+        <v>3</v>
+      </c>
+      <c r="T8" s="1">
+        <v>2</v>
+      </c>
+      <c r="U8" s="1">
+        <v>4</v>
+      </c>
+      <c r="V8" s="1">
         <v>1</v>
       </c>
-      <c r="T8" s="1">
-        <v>4</v>
-      </c>
-      <c r="U8" s="1">
-        <v>3</v>
-      </c>
-      <c r="V8" s="1">
-        <v>2</v>
-      </c>
       <c r="W8" s="1">
-        <v>4</v>
-      </c>
-      <c r="X8" s="1">
+        <v>5</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AJ8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK8" s="1">
         <v>1</v>
       </c>
-      <c r="Y8" s="1">
-        <v>5</v>
-      </c>
-      <c r="Z8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA8" s="1">
-        <v>5</v>
-      </c>
-      <c r="AB8" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC8" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK8" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="AL8" s="1" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="AM8" s="1">
-        <v>1</v>
-      </c>
-      <c r="AN8" s="1" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="AO8" s="1">
         <v>5</v>
       </c>
-      <c r="AQ8" s="1">
-        <v>5</v>
+      <c r="AP8" s="1">
+        <v>5</v>
+      </c>
+      <c r="AQ8" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AR8" s="1">
         <v>5</v>
       </c>
-      <c r="AS8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT8" s="1">
-        <v>5</v>
-      </c>
     </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>2020</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1">
+        <v>4</v>
+      </c>
+      <c r="D9" s="1">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1">
+        <v>4</v>
+      </c>
+      <c r="F9" s="1">
+        <v>5</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="1">
+        <v>5</v>
+      </c>
+      <c r="J9" s="1">
+        <v>5</v>
+      </c>
+      <c r="K9" s="1">
+        <v>5</v>
+      </c>
+      <c r="L9" s="1">
+        <v>5</v>
+      </c>
+      <c r="M9" s="1">
+        <v>5</v>
+      </c>
+      <c r="N9" s="1">
+        <v>4</v>
+      </c>
+      <c r="O9" s="1">
+        <v>3</v>
+      </c>
+      <c r="P9" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>2</v>
+      </c>
+      <c r="R9" s="1">
+        <v>4</v>
+      </c>
+      <c r="S9" s="1">
+        <v>4</v>
+      </c>
+      <c r="T9" s="1">
+        <v>5</v>
+      </c>
+      <c r="U9" s="1">
+        <v>1</v>
+      </c>
+      <c r="V9" s="1">
+        <v>1</v>
+      </c>
+      <c r="W9" s="1">
+        <v>4</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>3</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="1">
-        <v>4</v>
-      </c>
-      <c r="D9" s="1">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1">
-        <v>4</v>
-      </c>
-      <c r="F9" s="1">
-        <v>5</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I9" s="1">
-        <v>5</v>
-      </c>
-      <c r="J9" s="1">
-        <v>5</v>
-      </c>
-      <c r="K9" s="1">
-        <v>5</v>
-      </c>
-      <c r="L9" s="1">
-        <v>5</v>
-      </c>
-      <c r="M9" s="1">
-        <v>5</v>
-      </c>
-      <c r="N9" s="1">
-        <v>5</v>
-      </c>
-      <c r="O9" s="1">
-        <v>5</v>
-      </c>
-      <c r="P9" s="1">
-        <v>4</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>3</v>
-      </c>
-      <c r="R9" s="1">
-        <v>2</v>
-      </c>
-      <c r="S9" s="1">
-        <v>2</v>
-      </c>
-      <c r="T9" s="1">
-        <v>4</v>
-      </c>
-      <c r="U9" s="1">
-        <v>4</v>
-      </c>
-      <c r="V9" s="1">
-        <v>5</v>
-      </c>
-      <c r="W9" s="1">
-        <v>1</v>
-      </c>
-      <c r="X9" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="1">
-        <v>4</v>
-      </c>
-      <c r="Z9" s="1" t="s">
+      <c r="AK9" s="1">
+        <v>5</v>
+      </c>
+      <c r="AL9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AA9" s="1">
-        <v>3</v>
-      </c>
-      <c r="AB9" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC9" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE9" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AF9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AI9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AJ9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AL9" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="AM9" s="1">
-        <v>5</v>
-      </c>
-      <c r="AN9" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="AO9" s="1">
-        <v>4</v>
-      </c>
-      <c r="AQ9" s="1">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="AP9" s="1">
+        <v>4</v>
+      </c>
+      <c r="AQ9" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AR9" s="1">
-        <v>4</v>
-      </c>
-      <c r="AS9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT9" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>2019</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="D10" s="1">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1">
+        <v>3</v>
+      </c>
+      <c r="F10" s="1">
+        <v>4</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2</v>
+      </c>
+      <c r="H10" s="1">
+        <v>2</v>
+      </c>
+      <c r="I10" s="1">
+        <v>4</v>
+      </c>
+      <c r="J10" s="1">
+        <v>4</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="1">
+        <v>4</v>
+      </c>
+      <c r="M10" s="1">
+        <v>4</v>
+      </c>
+      <c r="N10" s="1">
+        <v>3</v>
+      </c>
+      <c r="O10" s="1">
+        <v>3</v>
+      </c>
+      <c r="P10" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>3</v>
+      </c>
+      <c r="R10" s="1">
+        <v>2</v>
+      </c>
+      <c r="S10" s="1">
+        <v>2</v>
+      </c>
+      <c r="T10" s="1">
+        <v>2</v>
+      </c>
+      <c r="U10" s="1">
+        <v>4</v>
+      </c>
+      <c r="V10" s="1">
+        <v>2</v>
+      </c>
+      <c r="W10" s="1">
+        <v>3</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>4</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AJ10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="1">
-        <v>4</v>
-      </c>
-      <c r="D10" s="1">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1">
-        <v>3</v>
-      </c>
-      <c r="F10" s="1">
-        <v>4</v>
-      </c>
-      <c r="G10" s="1">
-        <v>2</v>
-      </c>
-      <c r="H10" s="1">
-        <v>2</v>
-      </c>
-      <c r="I10" s="1">
-        <v>4</v>
-      </c>
-      <c r="J10" s="1">
-        <v>4</v>
-      </c>
-      <c r="K10" s="1">
-        <v>4</v>
-      </c>
-      <c r="L10" s="1">
-        <v>4</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="N10" s="1">
-        <v>4</v>
-      </c>
-      <c r="O10" s="1">
-        <v>4</v>
-      </c>
-      <c r="P10" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>3</v>
-      </c>
-      <c r="R10" s="1">
-        <v>3</v>
-      </c>
-      <c r="S10" s="1">
-        <v>3</v>
-      </c>
-      <c r="T10" s="1">
-        <v>2</v>
-      </c>
-      <c r="U10" s="1">
-        <v>2</v>
-      </c>
-      <c r="V10" s="1">
-        <v>2</v>
-      </c>
-      <c r="W10" s="1">
-        <v>4</v>
-      </c>
-      <c r="X10" s="1">
-        <v>2</v>
-      </c>
-      <c r="Y10" s="1">
-        <v>3</v>
-      </c>
-      <c r="Z10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA10" s="1">
-        <v>4</v>
-      </c>
-      <c r="AB10" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC10" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD10" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AF10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK10" s="1" t="s">
-        <v>52</v>
+      <c r="AK10" s="1">
+        <v>4</v>
       </c>
       <c r="AL10" s="1" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="AM10" s="1">
         <v>4</v>
       </c>
-      <c r="AN10" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="AO10" s="1">
         <v>4</v>
       </c>
-      <c r="AQ10" s="1">
-        <v>4</v>
+      <c r="AP10" s="1">
+        <v>4</v>
+      </c>
+      <c r="AQ10" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AR10" s="1">
         <v>4</v>
       </c>
-      <c r="AS10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT10" s="1">
-        <v>4</v>
-      </c>
     </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>2020</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C11" s="1">
         <v>5</v>
@@ -2030,13 +1965,13 @@
         <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="I11" s="1">
         <v>4</v>
@@ -2045,16 +1980,16 @@
         <v>5</v>
       </c>
       <c r="K11" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L11" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M11" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N11" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O11" s="1">
         <v>4</v>
@@ -2066,93 +2001,87 @@
         <v>4</v>
       </c>
       <c r="R11" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S11" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T11" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U11" s="1">
         <v>3</v>
       </c>
       <c r="V11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W11" s="1">
         <v>3</v>
       </c>
-      <c r="X11" s="1">
-        <v>1</v>
+      <c r="X11" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="Y11" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA11" s="1">
-        <v>4</v>
+        <v>25</v>
+      </c>
+      <c r="AA11" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC11" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="AD11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF11" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
+      </c>
+      <c r="AG11" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AI11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK11" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
+      </c>
+      <c r="AJ11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK11" s="1">
+        <v>3</v>
       </c>
       <c r="AL11" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AM11" s="1">
-        <v>3</v>
-      </c>
-      <c r="AN11" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="AO11" s="1">
-        <v>4</v>
-      </c>
-      <c r="AQ11" s="1">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="AP11" s="1">
+        <v>5</v>
+      </c>
+      <c r="AQ11" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AR11" s="1">
         <v>5</v>
       </c>
-      <c r="AS11" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AT11" s="1">
-        <v>5</v>
-      </c>
     </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>2019</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="F12" s="1">
         <v>3</v>
@@ -2167,108 +2096,102 @@
         <v>3</v>
       </c>
       <c r="J12" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L12" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M12" s="1">
+        <v>4</v>
+      </c>
+      <c r="N12" s="1">
+        <v>3</v>
+      </c>
+      <c r="O12" s="1">
+        <v>4</v>
+      </c>
+      <c r="P12" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>2</v>
+      </c>
+      <c r="R12" s="1">
+        <v>5</v>
+      </c>
+      <c r="S12" s="1">
+        <v>4</v>
+      </c>
+      <c r="T12" s="1">
+        <v>4</v>
+      </c>
+      <c r="U12" s="1">
+        <v>4</v>
+      </c>
+      <c r="V12" s="1">
         <v>1</v>
       </c>
-      <c r="N12" s="1">
-        <v>1</v>
-      </c>
-      <c r="O12" s="1">
-        <v>4</v>
-      </c>
-      <c r="P12" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>4</v>
-      </c>
-      <c r="R12" s="1">
-        <v>2</v>
-      </c>
-      <c r="S12" s="1">
-        <v>2</v>
-      </c>
-      <c r="T12" s="1">
-        <v>5</v>
-      </c>
-      <c r="U12" s="1">
-        <v>4</v>
-      </c>
-      <c r="V12" s="1">
-        <v>4</v>
-      </c>
       <c r="W12" s="1">
-        <v>4</v>
-      </c>
-      <c r="X12" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="1">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>52</v>
+        <v>37</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="AC12" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AD12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE12" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF12" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
+      </c>
+      <c r="AG12" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AI12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK12" s="1" t="s">
-        <v>57</v>
+        <v>34</v>
+      </c>
+      <c r="AJ12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK12" s="1">
+        <v>3</v>
       </c>
       <c r="AL12" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="AM12" s="1">
         <v>3</v>
       </c>
-      <c r="AN12" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="AO12" s="1">
-        <v>3</v>
-      </c>
-      <c r="AQ12" s="1">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="AP12" s="1">
+        <v>3</v>
+      </c>
+      <c r="AQ12" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AR12" s="1">
-        <v>3</v>
-      </c>
-      <c r="AS12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT12" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>2019</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
@@ -2292,22 +2215,22 @@
         <v>1</v>
       </c>
       <c r="J13" s="1">
-        <v>3</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
       </c>
       <c r="L13" s="1">
         <v>1</v>
       </c>
       <c r="M13" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N13" s="1">
         <v>1</v>
       </c>
       <c r="O13" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P13" s="1">
         <v>1</v>
@@ -2319,10 +2242,10 @@
         <v>1</v>
       </c>
       <c r="S13" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T13" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U13" s="1">
         <v>3</v>
@@ -2333,73 +2256,67 @@
       <c r="W13" s="1">
         <v>3</v>
       </c>
-      <c r="X13" s="1">
-        <v>3</v>
-      </c>
-      <c r="Y13" s="1">
-        <v>3</v>
+      <c r="X13" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="Z13" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="AA13" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="AB13" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC13" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="AD13" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
+      </c>
+      <c r="AE13" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AF13" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="AG13" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="AH13" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="AI13" s="1" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="AJ13" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK13" s="1" t="s">
-        <v>57</v>
+        <v>34</v>
+      </c>
+      <c r="AK13" s="1">
+        <v>5</v>
       </c>
       <c r="AL13" s="1" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AM13" s="1">
         <v>5</v>
       </c>
-      <c r="AN13" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="AO13" s="1">
-        <v>5</v>
-      </c>
-      <c r="AQ13" s="1">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="AP13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AQ13" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AR13" s="1">
-        <v>1</v>
-      </c>
-      <c r="AS13" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT13" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>2019</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C14" s="1">
         <v>5</v>
@@ -2408,22 +2325,22 @@
         <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="F14" s="1">
         <v>5</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="I14" s="1">
         <v>4</v>
       </c>
       <c r="J14" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K14" s="1">
         <v>5</v>
@@ -2432,7 +2349,7 @@
         <v>4</v>
       </c>
       <c r="M14" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N14" s="1">
         <v>4</v>
@@ -2441,96 +2358,90 @@
         <v>4</v>
       </c>
       <c r="P14" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q14" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R14" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S14" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T14" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U14" s="1">
         <v>3</v>
       </c>
       <c r="V14" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W14" s="1">
-        <v>3</v>
-      </c>
-      <c r="X14" s="1">
+        <v>5</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AJ14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK14" s="1">
         <v>1</v>
       </c>
-      <c r="Y14" s="1">
-        <v>5</v>
-      </c>
-      <c r="Z14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB14" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE14" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK14" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="AL14" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="AM14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AN14" s="1" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="AO14" s="1">
         <v>5</v>
       </c>
-      <c r="AQ14" s="1">
-        <v>5</v>
+      <c r="AP14" s="1">
+        <v>5</v>
+      </c>
+      <c r="AQ14" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AR14" s="1">
-        <v>5</v>
-      </c>
-      <c r="AS14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT14" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>2020</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
@@ -2554,13 +2465,13 @@
         <v>4</v>
       </c>
       <c r="J15" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K15" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L15" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M15" s="1">
         <v>4</v>
@@ -2578,227 +2489,215 @@
         <v>4</v>
       </c>
       <c r="R15" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S15" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U15" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V15" s="1">
         <v>3</v>
       </c>
       <c r="W15" s="1">
-        <v>4</v>
-      </c>
-      <c r="X15" s="1">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="Y15" s="1">
         <v>5</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA15" s="1">
-        <v>5</v>
+        <v>54</v>
+      </c>
+      <c r="AA15" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="AC15" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD15" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="AF15" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="AG15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH15" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="AI15" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK15" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
+      </c>
+      <c r="AJ15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK15" s="1">
+        <v>3</v>
       </c>
       <c r="AL15" s="1" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AM15" s="1">
         <v>3</v>
       </c>
-      <c r="AN15" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="AO15" s="1">
-        <v>3</v>
-      </c>
-      <c r="AQ15" s="1">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="AP15" s="1">
+        <v>5</v>
+      </c>
+      <c r="AQ15" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AR15" s="1">
         <v>5</v>
       </c>
-      <c r="AS15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AT15" s="1">
-        <v>5</v>
-      </c>
     </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>2019</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="1">
+        <v>5</v>
+      </c>
+      <c r="D16" s="1">
+        <v>5</v>
+      </c>
+      <c r="E16" s="1">
+        <v>3</v>
+      </c>
+      <c r="F16" s="1">
+        <v>4</v>
+      </c>
+      <c r="G16" s="1">
+        <v>5</v>
+      </c>
+      <c r="H16" s="1">
+        <v>5</v>
+      </c>
+      <c r="I16" s="1">
+        <v>3</v>
+      </c>
+      <c r="J16" s="1">
+        <v>3</v>
+      </c>
+      <c r="K16" s="1">
+        <v>4</v>
+      </c>
+      <c r="L16" s="1">
+        <v>4</v>
+      </c>
+      <c r="M16" s="1">
+        <v>5</v>
+      </c>
+      <c r="N16" s="1">
+        <v>4</v>
+      </c>
+      <c r="O16" s="1">
+        <v>4</v>
+      </c>
+      <c r="P16" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>4</v>
+      </c>
+      <c r="R16" s="1">
+        <v>5</v>
+      </c>
+      <c r="S16" s="1">
+        <v>4</v>
+      </c>
+      <c r="T16" s="1">
+        <v>5</v>
+      </c>
+      <c r="U16" s="1">
+        <v>5</v>
+      </c>
+      <c r="V16" s="1">
+        <v>3</v>
+      </c>
+      <c r="W16" s="1">
+        <v>5</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>4</v>
+      </c>
+      <c r="Z16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AJ16" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="1">
-        <v>5</v>
-      </c>
-      <c r="D16" s="1">
-        <v>5</v>
-      </c>
-      <c r="E16" s="1">
-        <v>3</v>
-      </c>
-      <c r="F16" s="1">
-        <v>4</v>
-      </c>
-      <c r="G16" s="1">
-        <v>5</v>
-      </c>
-      <c r="H16" s="1">
-        <v>5</v>
-      </c>
-      <c r="I16" s="1">
-        <v>3</v>
-      </c>
-      <c r="J16" s="1">
-        <v>3</v>
-      </c>
-      <c r="K16" s="1">
-        <v>3</v>
-      </c>
-      <c r="L16" s="1">
-        <v>3</v>
-      </c>
-      <c r="M16" s="1">
-        <v>4</v>
-      </c>
-      <c r="N16" s="1">
-        <v>4</v>
-      </c>
-      <c r="O16" s="1">
-        <v>5</v>
-      </c>
-      <c r="P16" s="1">
-        <v>4</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>4</v>
-      </c>
-      <c r="R16" s="1">
-        <v>3</v>
-      </c>
-      <c r="S16" s="1">
-        <v>4</v>
-      </c>
-      <c r="T16" s="1">
-        <v>5</v>
-      </c>
-      <c r="U16" s="1">
-        <v>4</v>
-      </c>
-      <c r="V16" s="1">
-        <v>5</v>
-      </c>
-      <c r="W16" s="1">
-        <v>5</v>
-      </c>
-      <c r="X16" s="1">
-        <v>3</v>
-      </c>
-      <c r="Y16" s="1">
-        <v>5</v>
-      </c>
-      <c r="Z16" s="1" t="s">
+      <c r="AK16" s="1">
+        <v>5</v>
+      </c>
+      <c r="AL16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AA16" s="1">
-        <v>4</v>
-      </c>
-      <c r="AB16" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC16" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF16" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG16" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI16" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AJ16" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AL16" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="AM16" s="1">
-        <v>5</v>
-      </c>
-      <c r="AN16" s="1" t="s">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="AO16" s="1">
-        <v>3</v>
-      </c>
-      <c r="AQ16" s="1">
-        <v>4</v>
+        <v>4</v>
+      </c>
+      <c r="AP16" s="1">
+        <v>5</v>
+      </c>
+      <c r="AQ16" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AR16" s="1">
-        <v>5</v>
-      </c>
-      <c r="AS16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT16" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>2019</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C17" s="1">
         <v>5</v>
@@ -2807,13 +2706,13 @@
         <v>5</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="F17" s="1">
         <v>4</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="H17" s="1">
         <v>2</v>
@@ -2825,105 +2724,99 @@
         <v>5</v>
       </c>
       <c r="K17" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L17" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M17" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N17" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O17" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P17" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R17" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S17" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T17" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U17" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V17" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W17" s="1">
-        <v>3</v>
-      </c>
-      <c r="X17" s="1">
-        <v>2</v>
-      </c>
-      <c r="Y17" s="1">
-        <v>4</v>
+        <v>4</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
+      </c>
+      <c r="AA17" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="AC17" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="AD17" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE17" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AF17" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
+      </c>
+      <c r="AG17" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AI17" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK17" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
+      </c>
+      <c r="AJ17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK17" s="1">
+        <v>4</v>
       </c>
       <c r="AL17" s="1" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="AM17" s="1">
-        <v>4</v>
-      </c>
-      <c r="AN17" s="1" t="s">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="AO17" s="1">
-        <v>3</v>
-      </c>
-      <c r="AQ17" s="1">
-        <v>4</v>
+        <v>4</v>
+      </c>
+      <c r="AP17" s="1">
+        <v>4</v>
+      </c>
+      <c r="AQ17" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AR17" s="1">
         <v>4</v>
       </c>
-      <c r="AS17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AT17" s="1">
-        <v>4</v>
-      </c>
     </row>
-    <row r="18" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>2019</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C18" s="1">
         <v>5</v>
@@ -2932,7 +2825,7 @@
         <v>5</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="F18" s="1">
         <v>4</v>
@@ -2941,7 +2834,7 @@
         <v>4</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="I18" s="1">
         <v>5</v>
@@ -2950,7 +2843,7 @@
         <v>5</v>
       </c>
       <c r="K18" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L18" s="1">
         <v>5</v>
@@ -2962,16 +2855,16 @@
         <v>5</v>
       </c>
       <c r="O18" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P18" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="1">
         <v>4</v>
       </c>
       <c r="R18" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S18" s="1">
         <v>4</v>
@@ -2980,81 +2873,75 @@
         <v>5</v>
       </c>
       <c r="U18" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V18" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W18" s="1">
-        <v>3</v>
-      </c>
-      <c r="X18" s="1">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="Y18" s="1">
         <v>5</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA18" s="1">
-        <v>5</v>
+        <v>60</v>
+      </c>
+      <c r="AA18" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC18" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="AD18" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
+      </c>
+      <c r="AE18" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AF18" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="AG18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH18" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="AI18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK18" s="1" t="s">
-        <v>84</v>
+        <v>61</v>
+      </c>
+      <c r="AJ18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK18" s="1">
+        <v>4</v>
       </c>
       <c r="AL18" s="1" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="AM18" s="1">
-        <v>4</v>
-      </c>
-      <c r="AN18" s="1" t="s">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="AO18" s="1">
         <v>3</v>
       </c>
-      <c r="AQ18" s="1">
-        <v>3</v>
+      <c r="AP18" s="1">
+        <v>3</v>
+      </c>
+      <c r="AQ18" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AR18" s="1">
         <v>3</v>
       </c>
-      <c r="AS18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT18" s="1">
-        <v>3</v>
-      </c>
     </row>
-    <row r="19" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>2020</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C19" s="1">
         <v>3</v>
@@ -3063,34 +2950,34 @@
         <v>4</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="G19" s="1">
         <v>4</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="I19" s="1">
         <v>3</v>
       </c>
-      <c r="J19" s="1">
-        <v>4</v>
-      </c>
-      <c r="K19" s="1">
-        <v>3</v>
+      <c r="J19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>66</v>
+        <v>43</v>
+      </c>
+      <c r="M19" s="1">
+        <v>2</v>
+      </c>
+      <c r="N19" s="1">
+        <v>2</v>
       </c>
       <c r="O19" s="1">
         <v>2</v>
@@ -3099,93 +2986,87 @@
         <v>2</v>
       </c>
       <c r="Q19" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R19" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S19" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T19" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U19" s="1">
         <v>4</v>
       </c>
       <c r="V19" s="1">
+        <v>2</v>
+      </c>
+      <c r="W19" s="1">
+        <v>4</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y19" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AJ19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK19" s="1">
+        <v>3</v>
+      </c>
+      <c r="AL19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM19" s="1">
+        <v>3</v>
+      </c>
+      <c r="AO19" s="1">
         <v>1</v>
       </c>
-      <c r="W19" s="1">
-        <v>4</v>
-      </c>
-      <c r="X19" s="1">
-        <v>2</v>
-      </c>
-      <c r="Y19" s="1">
-        <v>4</v>
-      </c>
-      <c r="Z19" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA19" s="1">
-        <v>5</v>
-      </c>
-      <c r="AB19" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC19" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AD19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF19" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG19" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AL19" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AM19" s="1">
-        <v>3</v>
-      </c>
-      <c r="AN19" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AO19" s="1">
-        <v>3</v>
-      </c>
-      <c r="AQ19" s="1">
-        <v>1</v>
+      <c r="AP19" s="1">
+        <v>2</v>
+      </c>
+      <c r="AQ19" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AR19" s="1">
         <v>2</v>
       </c>
-      <c r="AS19" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AT19" s="1">
-        <v>2</v>
-      </c>
     </row>
-    <row r="20" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>2019</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C20" s="1">
         <v>5</v>
@@ -3209,19 +3090,19 @@
         <v>5</v>
       </c>
       <c r="J20" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K20" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L20" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M20" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N20" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O20" s="1">
         <v>4</v>
@@ -3233,215 +3114,203 @@
         <v>4</v>
       </c>
       <c r="R20" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S20" s="1">
         <v>4</v>
       </c>
       <c r="T20" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U20" s="1">
         <v>4</v>
       </c>
       <c r="V20" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W20" s="1">
-        <v>4</v>
-      </c>
-      <c r="X20" s="1">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="Y20" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA20" s="1">
-        <v>5</v>
+        <v>25</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB20" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC20" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="AD20" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
+      </c>
+      <c r="AE20" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AF20" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="AG20" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="AH20" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="AI20" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="AJ20" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK20" s="1" t="s">
-        <v>52</v>
+        <v>34</v>
+      </c>
+      <c r="AK20" s="1">
+        <v>4</v>
       </c>
       <c r="AL20" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="AM20" s="1">
         <v>4</v>
       </c>
-      <c r="AN20" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="AO20" s="1">
-        <v>4</v>
-      </c>
-      <c r="AQ20" s="1">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="AP20" s="1">
+        <v>4</v>
+      </c>
+      <c r="AQ20" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AR20" s="1">
-        <v>4</v>
-      </c>
-      <c r="AS20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT20" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>2018</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="1">
+        <v>5</v>
+      </c>
+      <c r="D21" s="1">
+        <v>5</v>
+      </c>
+      <c r="E21" s="1">
+        <v>3</v>
+      </c>
+      <c r="F21" s="1">
+        <v>3</v>
+      </c>
+      <c r="G21" s="1">
+        <v>3</v>
+      </c>
+      <c r="H21" s="1">
+        <v>2</v>
+      </c>
+      <c r="I21" s="1">
+        <v>5</v>
+      </c>
+      <c r="J21" s="1">
+        <v>5</v>
+      </c>
+      <c r="K21" s="1">
+        <v>5</v>
+      </c>
+      <c r="L21" s="1">
+        <v>4</v>
+      </c>
+      <c r="M21" s="1">
+        <v>5</v>
+      </c>
+      <c r="N21" s="1">
+        <v>4</v>
+      </c>
+      <c r="O21" s="1">
+        <v>4</v>
+      </c>
+      <c r="P21" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>4</v>
+      </c>
+      <c r="R21" s="1">
+        <v>5</v>
+      </c>
+      <c r="S21" s="1">
+        <v>3</v>
+      </c>
+      <c r="T21" s="1">
+        <v>5</v>
+      </c>
+      <c r="U21" s="1">
+        <v>4</v>
+      </c>
+      <c r="V21" s="1">
+        <v>1</v>
+      </c>
+      <c r="W21" s="1">
+        <v>4</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AJ21" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="1">
-        <v>5</v>
-      </c>
-      <c r="D21" s="1">
-        <v>5</v>
-      </c>
-      <c r="E21" s="1">
-        <v>3</v>
-      </c>
-      <c r="F21" s="1">
-        <v>3</v>
-      </c>
-      <c r="G21" s="1">
-        <v>3</v>
-      </c>
-      <c r="H21" s="1">
-        <v>2</v>
-      </c>
-      <c r="I21" s="1">
-        <v>5</v>
-      </c>
-      <c r="J21" s="1">
-        <v>5</v>
-      </c>
-      <c r="K21" s="1">
-        <v>5</v>
-      </c>
-      <c r="L21" s="1">
-        <v>5</v>
-      </c>
-      <c r="M21" s="1">
-        <v>5</v>
-      </c>
-      <c r="N21" s="1">
-        <v>4</v>
-      </c>
-      <c r="O21" s="1">
-        <v>5</v>
-      </c>
-      <c r="P21" s="1">
-        <v>4</v>
-      </c>
-      <c r="Q21" s="1">
-        <v>4</v>
-      </c>
-      <c r="R21" s="1">
-        <v>4</v>
-      </c>
-      <c r="S21" s="1">
-        <v>4</v>
-      </c>
-      <c r="T21" s="1">
-        <v>5</v>
-      </c>
-      <c r="U21" s="1">
-        <v>3</v>
-      </c>
-      <c r="V21" s="1">
-        <v>5</v>
-      </c>
-      <c r="W21" s="1">
-        <v>4</v>
-      </c>
-      <c r="X21" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y21" s="1">
-        <v>4</v>
-      </c>
-      <c r="Z21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB21" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK21" s="1" t="s">
-        <v>52</v>
+      <c r="AK21" s="1">
+        <v>3</v>
       </c>
       <c r="AL21" s="1" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="AM21" s="1">
         <v>3</v>
       </c>
-      <c r="AN21" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="AO21" s="1">
-        <v>3</v>
-      </c>
-      <c r="AQ21" s="1">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="AP21" s="1">
+        <v>4</v>
+      </c>
+      <c r="AQ21" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AR21" s="1">
-        <v>4</v>
-      </c>
-      <c r="AS21" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AT21" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>2019</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
@@ -3465,7 +3334,7 @@
         <v>4</v>
       </c>
       <c r="J22" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K22" s="1">
         <v>1</v>
@@ -3474,13 +3343,13 @@
         <v>1</v>
       </c>
       <c r="M22" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N22" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O22" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P22" s="1">
         <v>5</v>
@@ -3489,84 +3358,78 @@
         <v>5</v>
       </c>
       <c r="R22" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S22" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T22" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U22" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V22" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W22" s="1">
         <v>5</v>
       </c>
-      <c r="X22" s="1">
-        <v>2</v>
-      </c>
-      <c r="Y22" s="1">
-        <v>5</v>
+      <c r="X22" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>52</v>
+        <v>25</v>
+      </c>
+      <c r="AA22" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AC22" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE22" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AF22" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
+      </c>
+      <c r="AG22" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AI22" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK22" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
+      </c>
+      <c r="AJ22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK22" s="1">
+        <v>5</v>
       </c>
       <c r="AL22" s="1" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="AM22" s="1">
-        <v>5</v>
-      </c>
-      <c r="AN22" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="AO22" s="1">
-        <v>4</v>
-      </c>
-      <c r="AQ22" s="1">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="AP22" s="1">
+        <v>2</v>
+      </c>
+      <c r="AQ22" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AR22" s="1">
-        <v>2</v>
-      </c>
-      <c r="AS22" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AT22" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>2020</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C23" s="1">
         <v>5</v>
@@ -3602,10 +3465,10 @@
         <v>4</v>
       </c>
       <c r="N23" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O23" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P23" s="1">
         <v>3</v>
@@ -3620,221 +3483,209 @@
         <v>3</v>
       </c>
       <c r="T23" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U23" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V23" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W23" s="1">
         <v>4</v>
       </c>
-      <c r="X23" s="1">
-        <v>3</v>
+      <c r="X23" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="Y23" s="1">
         <v>4</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA23" s="1">
-        <v>4</v>
+        <v>54</v>
+      </c>
+      <c r="AA23" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="AC23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI23" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AD23" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE23" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AF23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH23" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI23" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK23" s="1" t="s">
-        <v>87</v>
+      <c r="AJ23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK23" s="1">
+        <v>4</v>
       </c>
       <c r="AL23" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="AM23" s="1">
-        <v>4</v>
-      </c>
-      <c r="AN23" s="1" t="s">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="AO23" s="1">
-        <v>3</v>
-      </c>
-      <c r="AQ23" s="1">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="AP23" s="1">
+        <v>4</v>
+      </c>
+      <c r="AQ23" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AR23" s="1">
-        <v>4</v>
-      </c>
-      <c r="AS23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AT23" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>2021</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="1">
+        <v>5</v>
+      </c>
+      <c r="D24" s="1">
+        <v>5</v>
+      </c>
+      <c r="E24" s="1">
+        <v>5</v>
+      </c>
+      <c r="F24" s="1">
+        <v>5</v>
+      </c>
+      <c r="G24" s="1">
+        <v>5</v>
+      </c>
+      <c r="H24" s="1">
+        <v>5</v>
+      </c>
+      <c r="I24" s="1">
+        <v>5</v>
+      </c>
+      <c r="J24" s="1">
+        <v>3</v>
+      </c>
+      <c r="K24" s="1">
+        <v>5</v>
+      </c>
+      <c r="L24" s="1">
+        <v>5</v>
+      </c>
+      <c r="M24" s="1">
+        <v>4</v>
+      </c>
+      <c r="N24" s="1">
+        <v>4</v>
+      </c>
+      <c r="O24" s="1">
+        <v>4</v>
+      </c>
+      <c r="P24" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>3</v>
+      </c>
+      <c r="R24" s="1">
+        <v>4</v>
+      </c>
+      <c r="S24" s="1">
+        <v>5</v>
+      </c>
+      <c r="T24" s="1">
+        <v>5</v>
+      </c>
+      <c r="U24" s="1">
+        <v>5</v>
+      </c>
+      <c r="V24" s="1">
+        <v>5</v>
+      </c>
+      <c r="W24" s="1">
+        <v>5</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y24" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AJ24" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="1">
-        <v>5</v>
-      </c>
-      <c r="D24" s="1">
-        <v>5</v>
-      </c>
-      <c r="E24" s="1">
-        <v>5</v>
-      </c>
-      <c r="F24" s="1">
-        <v>5</v>
-      </c>
-      <c r="G24" s="1">
-        <v>5</v>
-      </c>
-      <c r="H24" s="1">
-        <v>5</v>
-      </c>
-      <c r="I24" s="1">
-        <v>5</v>
-      </c>
-      <c r="J24" s="1">
-        <v>4</v>
-      </c>
-      <c r="K24" s="1">
-        <v>5</v>
-      </c>
-      <c r="L24" s="1">
-        <v>3</v>
-      </c>
-      <c r="M24" s="1">
-        <v>5</v>
-      </c>
-      <c r="N24" s="1">
-        <v>5</v>
-      </c>
-      <c r="O24" s="1">
-        <v>4</v>
-      </c>
-      <c r="P24" s="1">
-        <v>4</v>
-      </c>
-      <c r="Q24" s="1">
-        <v>4</v>
-      </c>
-      <c r="R24" s="1">
-        <v>3</v>
-      </c>
-      <c r="S24" s="1">
-        <v>3</v>
-      </c>
-      <c r="T24" s="1">
-        <v>4</v>
-      </c>
-      <c r="U24" s="1">
-        <v>5</v>
-      </c>
-      <c r="V24" s="1">
-        <v>5</v>
-      </c>
-      <c r="W24" s="1">
-        <v>5</v>
-      </c>
-      <c r="X24" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y24" s="1">
-        <v>5</v>
-      </c>
-      <c r="Z24" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA24" s="1">
-        <v>5</v>
-      </c>
-      <c r="AB24" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC24" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD24" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF24" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG24" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH24" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI24" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AJ24" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK24" s="1" t="s">
-        <v>52</v>
+      <c r="AK24" s="1">
+        <v>5</v>
       </c>
       <c r="AL24" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="AM24" s="1">
         <v>5</v>
       </c>
-      <c r="AN24" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="AO24" s="1">
-        <v>5</v>
-      </c>
-      <c r="AQ24" s="1">
-        <v>4</v>
+        <v>4</v>
+      </c>
+      <c r="AP24" s="1">
+        <v>4</v>
+      </c>
+      <c r="AQ24" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AR24" s="1">
         <v>4</v>
       </c>
-      <c r="AS24" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT24" s="1">
-        <v>4</v>
-      </c>
     </row>
-    <row r="25" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>2019</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C25" s="1">
         <v>4</v>
@@ -3858,376 +3709,358 @@
         <v>5</v>
       </c>
       <c r="J25" s="1">
-        <v>5</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="L25" s="1">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="K25" s="1">
+        <v>4</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M25" s="1">
-        <v>4</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>66</v>
+        <v>3</v>
+      </c>
+      <c r="N25" s="1">
+        <v>4</v>
       </c>
       <c r="O25" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P25" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q25" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R25" s="1">
         <v>3</v>
       </c>
       <c r="S25" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T25" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U25" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V25" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W25" s="1">
-        <v>5</v>
-      </c>
-      <c r="X25" s="1">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="Y25" s="1">
         <v>4</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA25" s="1">
-        <v>4</v>
+        <v>37</v>
+      </c>
+      <c r="AA25" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AB25" s="1" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="AC25" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AD25" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="AE25" s="1" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="AF25" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="AG25" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH25" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="AI25" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK25" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
+      </c>
+      <c r="AJ25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK25" s="1">
+        <v>2</v>
       </c>
       <c r="AL25" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="AM25" s="1">
-        <v>2</v>
-      </c>
-      <c r="AN25" s="1" t="s">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="AO25" s="1">
-        <v>3</v>
-      </c>
-      <c r="AQ25" s="1">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="AP25" s="1">
+        <v>4</v>
+      </c>
+      <c r="AQ25" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AR25" s="1">
-        <v>4</v>
-      </c>
-      <c r="AS25" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT25" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>2019</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="1">
+        <v>4</v>
+      </c>
+      <c r="D26" s="1">
+        <v>4</v>
+      </c>
+      <c r="E26" s="1">
+        <v>3</v>
+      </c>
+      <c r="F26" s="1">
+        <v>3</v>
+      </c>
+      <c r="G26" s="1">
+        <v>3</v>
+      </c>
+      <c r="H26" s="1">
+        <v>3</v>
+      </c>
+      <c r="I26" s="1">
+        <v>3</v>
+      </c>
+      <c r="J26" s="1">
+        <v>3</v>
+      </c>
+      <c r="K26" s="1">
+        <v>3</v>
+      </c>
+      <c r="L26" s="1">
+        <v>3</v>
+      </c>
+      <c r="M26" s="1">
+        <v>3</v>
+      </c>
+      <c r="N26" s="1">
+        <v>3</v>
+      </c>
+      <c r="O26" s="1">
+        <v>4</v>
+      </c>
+      <c r="P26" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>4</v>
+      </c>
+      <c r="R26" s="1">
+        <v>4</v>
+      </c>
+      <c r="S26" s="1">
+        <v>3</v>
+      </c>
+      <c r="T26" s="1">
+        <v>4</v>
+      </c>
+      <c r="U26" s="1">
+        <v>5</v>
+      </c>
+      <c r="V26" s="1">
+        <v>5</v>
+      </c>
+      <c r="W26" s="1">
+        <v>3</v>
+      </c>
+      <c r="X26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y26" s="1">
+        <v>4</v>
+      </c>
+      <c r="Z26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AJ26" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="1">
-        <v>4</v>
-      </c>
-      <c r="D26" s="1">
-        <v>4</v>
-      </c>
-      <c r="E26" s="1">
-        <v>3</v>
-      </c>
-      <c r="F26" s="1">
-        <v>3</v>
-      </c>
-      <c r="G26" s="1">
-        <v>3</v>
-      </c>
-      <c r="H26" s="1">
-        <v>3</v>
-      </c>
-      <c r="I26" s="1">
-        <v>3</v>
-      </c>
-      <c r="J26" s="1">
-        <v>4</v>
-      </c>
-      <c r="K26" s="1">
-        <v>4</v>
-      </c>
-      <c r="L26" s="1">
-        <v>3</v>
-      </c>
-      <c r="M26" s="1">
-        <v>3</v>
-      </c>
-      <c r="N26" s="1">
-        <v>3</v>
-      </c>
-      <c r="O26" s="1">
-        <v>3</v>
-      </c>
-      <c r="P26" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>4</v>
-      </c>
-      <c r="R26" s="1">
-        <v>4</v>
-      </c>
-      <c r="S26" s="1">
-        <v>4</v>
-      </c>
-      <c r="T26" s="1">
-        <v>4</v>
-      </c>
-      <c r="U26" s="1">
-        <v>3</v>
-      </c>
-      <c r="V26" s="1">
-        <v>4</v>
-      </c>
-      <c r="W26" s="1">
-        <v>5</v>
-      </c>
-      <c r="X26" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y26" s="1">
-        <v>3</v>
-      </c>
-      <c r="Z26" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA26" s="1">
-        <v>4</v>
-      </c>
-      <c r="AB26" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AC26" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD26" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF26" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG26" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH26" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI26" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK26" s="1" t="s">
-        <v>52</v>
+      <c r="AK26" s="1">
+        <v>2</v>
       </c>
       <c r="AL26" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="AM26" s="1">
-        <v>2</v>
-      </c>
-      <c r="AN26" s="1" t="s">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="AO26" s="1">
         <v>3</v>
       </c>
-      <c r="AQ26" s="1">
-        <v>3</v>
+      <c r="AP26" s="1">
+        <v>4</v>
+      </c>
+      <c r="AQ26" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AR26" s="1">
         <v>4</v>
       </c>
-      <c r="AS26" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT26" s="1">
-        <v>4</v>
-      </c>
     </row>
-    <row r="27" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>2019</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="1">
+        <v>4</v>
+      </c>
+      <c r="D27" s="1">
+        <v>5</v>
+      </c>
+      <c r="E27" s="1">
+        <v>5</v>
+      </c>
+      <c r="F27" s="1">
+        <v>4</v>
+      </c>
+      <c r="G27" s="1">
+        <v>4</v>
+      </c>
+      <c r="H27" s="1">
+        <v>4</v>
+      </c>
+      <c r="I27" s="1">
+        <v>5</v>
+      </c>
+      <c r="J27" s="1">
+        <v>4</v>
+      </c>
+      <c r="K27" s="1">
+        <v>5</v>
+      </c>
+      <c r="L27" s="1">
+        <v>4</v>
+      </c>
+      <c r="M27" s="1">
+        <v>4</v>
+      </c>
+      <c r="N27" s="1">
+        <v>3</v>
+      </c>
+      <c r="O27" s="1">
+        <v>3</v>
+      </c>
+      <c r="P27" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>4</v>
+      </c>
+      <c r="R27" s="1">
+        <v>5</v>
+      </c>
+      <c r="S27" s="1">
+        <v>4</v>
+      </c>
+      <c r="T27" s="1">
+        <v>5</v>
+      </c>
+      <c r="U27" s="1">
+        <v>4</v>
+      </c>
+      <c r="V27" s="1">
+        <v>1</v>
+      </c>
+      <c r="W27" s="1">
+        <v>4</v>
+      </c>
+      <c r="X27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y27" s="1">
+        <v>4</v>
+      </c>
+      <c r="Z27" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI27" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="1">
-        <v>4</v>
-      </c>
-      <c r="D27" s="1">
-        <v>5</v>
-      </c>
-      <c r="E27" s="1">
-        <v>5</v>
-      </c>
-      <c r="F27" s="1">
-        <v>4</v>
-      </c>
-      <c r="G27" s="1">
-        <v>4</v>
-      </c>
-      <c r="H27" s="1">
-        <v>4</v>
-      </c>
-      <c r="I27" s="1">
-        <v>5</v>
-      </c>
-      <c r="J27" s="1">
-        <v>5</v>
-      </c>
-      <c r="K27" s="1">
-        <v>4</v>
-      </c>
-      <c r="L27" s="1">
-        <v>4</v>
-      </c>
-      <c r="M27" s="1">
-        <v>5</v>
-      </c>
-      <c r="N27" s="1">
-        <v>4</v>
-      </c>
-      <c r="O27" s="1">
-        <v>4</v>
-      </c>
-      <c r="P27" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="1">
-        <v>3</v>
-      </c>
-      <c r="R27" s="1">
-        <v>3</v>
-      </c>
-      <c r="S27" s="1">
-        <v>4</v>
-      </c>
-      <c r="T27" s="1">
-        <v>5</v>
-      </c>
-      <c r="U27" s="1">
-        <v>4</v>
-      </c>
-      <c r="V27" s="1">
-        <v>5</v>
-      </c>
-      <c r="W27" s="1">
-        <v>4</v>
-      </c>
-      <c r="X27" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y27" s="1">
-        <v>4</v>
-      </c>
-      <c r="Z27" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA27" s="1">
-        <v>4</v>
-      </c>
-      <c r="AB27" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC27" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE27" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AF27" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG27" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI27" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="AJ27" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK27" s="1" t="s">
-        <v>69</v>
+        <v>46</v>
+      </c>
+      <c r="AK27" s="1">
+        <v>4</v>
       </c>
       <c r="AL27" s="1" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="AM27" s="1">
         <v>4</v>
       </c>
-      <c r="AN27" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="AO27" s="1">
-        <v>4</v>
-      </c>
-      <c r="AQ27" s="1">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="AP27" s="1">
+        <v>4</v>
+      </c>
+      <c r="AQ27" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="AR27" s="1">
-        <v>4</v>
-      </c>
-      <c r="AS27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT27" s="1">
         <v>2</v>
       </c>
     </row>
